--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484110_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484110_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.1488</v>
+        <v>1.4905</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.4353</v>
+        <v>-0.6167</v>
       </c>
       <c r="F2" t="n">
-        <v>2.5842</v>
+        <v>2.1072</v>
       </c>
       <c r="G2" t="n">
         <v>-0.798</v>
@@ -610,13 +610,13 @@
         <v>2.579</v>
       </c>
       <c r="S2" t="n">
-        <v>1.3598</v>
+        <v>0.7014</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0625</v>
+        <v>-0.1189</v>
       </c>
       <c r="U2" t="n">
-        <v>1.2973</v>
+        <v>0.8203</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.793</v>
+        <v>0.367</v>
       </c>
       <c r="E3" t="n">
-        <v>1.5724</v>
+        <v>1.0623</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.7794</v>
+        <v>-0.6952</v>
       </c>
       <c r="G3" t="n">
         <v>1.1676</v>
@@ -688,13 +688,13 @@
         <v>1.3887</v>
       </c>
       <c r="S3" t="n">
-        <v>0.895</v>
+        <v>0.4691</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9467</v>
+        <v>0.4365</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0516</v>
+        <v>0.0325</v>
       </c>
       <c r="V3" t="n">
         <v>-0.6745</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. GUILLEN VIVES</t>
+          <t>E. GANDOL COBO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1674</v>
+        <v>0.136</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.3245</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0.492</v>
+        <v>0.136</v>
       </c>
       <c r="G4" t="n">
-        <v>1.2463</v>
+        <v>0.136</v>
       </c>
       <c r="H4" t="n">
-        <v>1.784</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5377</v>
+        <v>0.136</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2876</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9678</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.6802</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0.9588</v>
+        <v>0.136</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8162</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1425</v>
+        <v>0.136</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9919</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1276</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3798</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2523</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.2065</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.2065</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E. GANDOL COBO</t>
+          <t>D. GUILLEN VIVES</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.136</v>
+        <v>0.1037</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>-0.5286</v>
       </c>
       <c r="F5" t="n">
-        <v>0.136</v>
+        <v>0.6323</v>
       </c>
       <c r="G5" t="n">
-        <v>0.136</v>
+        <v>1.2463</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1.784</v>
       </c>
       <c r="I5" t="n">
-        <v>0.136</v>
+        <v>-0.5377</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>0.2876</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>0.9678</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-0.6802</v>
       </c>
       <c r="M5" t="n">
-        <v>0.136</v>
+        <v>0.9588</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>0.8162</v>
       </c>
       <c r="O5" t="n">
-        <v>0.136</v>
+        <v>0.1425</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>0.9919</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>0.0638</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>0.1758</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>-0.112</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-1.2065</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. AMABILINO PEREZ</t>
+          <t>D. IRUELA RUBIO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.929</v>
+        <v>-0.3577</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.3884</v>
+        <v>0.1511</v>
       </c>
       <c r="F6" t="n">
-        <v>1.4594</v>
+        <v>-0.5088</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.3267</v>
+        <v>0.4213</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.6751</v>
+        <v>-1.2901</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3485</v>
+        <v>1.7114</v>
       </c>
       <c r="J6" t="n">
-        <v>1.4982</v>
+        <v>2.2033</v>
       </c>
       <c r="K6" t="n">
-        <v>0.243</v>
+        <v>-0.2918</v>
       </c>
       <c r="L6" t="n">
-        <v>1.2552</v>
+        <v>2.4951</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.8248</v>
+        <v>-1.782</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.9181</v>
+        <v>-0.9983</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.9068000000000001</v>
+        <v>-0.7837</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.1903</v>
+        <v>-0.1984</v>
       </c>
       <c r="Q6" t="n">
-        <v>-4.3645</v>
+        <v>-2.3806</v>
       </c>
       <c r="R6" t="n">
-        <v>3.1741</v>
+        <v>2.1822</v>
       </c>
       <c r="S6" t="n">
-        <v>0.322</v>
+        <v>0.36</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6574</v>
+        <v>0.0625</v>
       </c>
       <c r="U6" t="n">
-        <v>0.9792999999999999</v>
+        <v>0.2975</v>
       </c>
       <c r="V6" t="n">
+        <v>-0.9405</v>
+      </c>
+      <c r="W6" t="n">
         <v>0.266</v>
       </c>
-      <c r="W6" t="n">
-        <v>1.1352</v>
-      </c>
       <c r="X6" t="n">
-        <v>-0.8692</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. IRUELA RUBIO</t>
+          <t>A. AMABILINO PEREZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.0282</v>
+        <v>-0.3596</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.6878</v>
+        <v>-1.7536</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3404</v>
+        <v>1.3939</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4213</v>
+        <v>-0.3267</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.2901</v>
+        <v>-0.6751</v>
       </c>
       <c r="I7" t="n">
-        <v>1.7114</v>
+        <v>0.3485</v>
       </c>
       <c r="J7" t="n">
-        <v>2.2033</v>
+        <v>1.4982</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.2918</v>
+        <v>0.243</v>
       </c>
       <c r="L7" t="n">
-        <v>2.4951</v>
+        <v>1.2552</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.782</v>
+        <v>-1.8248</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.9983</v>
+        <v>-0.9181</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.7837</v>
+        <v>-0.9068000000000001</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.1984</v>
+        <v>-1.1903</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.3806</v>
+        <v>-4.3645</v>
       </c>
       <c r="R7" t="n">
-        <v>2.1822</v>
+        <v>3.1741</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3106</v>
+        <v>0.8913</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7764</v>
+        <v>-0.0225</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4658</v>
+        <v>0.9137999999999999</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.9405</v>
+        <v>0.266</v>
       </c>
       <c r="W7" t="n">
-        <v>0.266</v>
+        <v>1.1352</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2065</v>
+        <v>-0.8692</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.2055</v>
+        <v>-1.4507</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.1299</v>
+        <v>-2.5154</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9244</v>
+        <v>1.0647</v>
       </c>
       <c r="G8" t="n">
         <v>-1.2943</v>
@@ -1078,13 +1078,13 @@
         <v>1.7855</v>
       </c>
       <c r="S8" t="n">
-        <v>0.224</v>
+        <v>-0.0212</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4479</v>
+        <v>0.0625</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.224</v>
+        <v>-0.0837</v>
       </c>
       <c r="V8" t="n">
         <v>-0.532</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S. CASAÚ PUEYO</t>
+          <t>F. LOPEZ BARCELO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.0726</v>
+        <v>-2.1635</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.1494</v>
+        <v>0.1005</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.9231</v>
+        <v>-2.2641</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3341</v>
+        <v>-2.9751</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.8271</v>
+        <v>-2.3532</v>
       </c>
       <c r="I9" t="n">
-        <v>3.1612</v>
+        <v>-0.6219</v>
       </c>
       <c r="J9" t="n">
-        <v>1.5031</v>
+        <v>-0.4424</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.6321</v>
+        <v>-1.0123</v>
       </c>
       <c r="L9" t="n">
-        <v>3.1352</v>
+        <v>0.5699</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.169</v>
+        <v>-2.5327</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.195</v>
+        <v>-1.3408</v>
       </c>
       <c r="O9" t="n">
-        <v>0.026</v>
+        <v>-1.1918</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.9838</v>
+        <v>0.3968</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.3725</v>
+        <v>-0.9919</v>
       </c>
       <c r="R9" t="n">
         <v>1.3887</v>
       </c>
       <c r="S9" t="n">
-        <v>1.3156</v>
+        <v>0.1488</v>
       </c>
       <c r="T9" t="n">
-        <v>0.72</v>
+        <v>0.0624</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5956</v>
+        <v>0.0864</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.7384</v>
+        <v>0.266</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.4724</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.7384</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>F. LOPEZ BARCELO</t>
+          <t>S. CASAÚ PUEYO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.916</v>
+        <v>-2.222</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.5117</v>
+        <v>-1.4952</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.4043</v>
+        <v>-0.7267</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.9751</v>
+        <v>0.3341</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.3532</v>
+        <v>-2.8271</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.6219</v>
+        <v>3.1612</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.4424</v>
+        <v>1.5031</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.0123</v>
+        <v>-1.6321</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5699</v>
+        <v>3.1352</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.5327</v>
+        <v>-1.169</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.3408</v>
+        <v>-1.195</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.1918</v>
+        <v>0.026</v>
       </c>
       <c r="P10" t="n">
-        <v>0.3968</v>
+        <v>-1.9838</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9919</v>
+        <v>-3.3725</v>
       </c>
       <c r="R10" t="n">
         <v>1.3887</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6036</v>
+        <v>1.1662</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5498</v>
+        <v>0.3742</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0539</v>
+        <v>0.792</v>
       </c>
       <c r="V10" t="n">
-        <v>0.266</v>
+        <v>-1.7384</v>
       </c>
       <c r="W10" t="n">
-        <v>1.4724</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2065</v>
+        <v>-1.7384</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.9818</v>
+        <v>-2.7038</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.1236</v>
+        <v>-3.8175</v>
       </c>
       <c r="F11" t="n">
-        <v>1.1417</v>
+        <v>1.1137</v>
       </c>
       <c r="G11" t="n">
         <v>-1.7506</v>
@@ -1312,13 +1312,13 @@
         <v>0.9919</v>
       </c>
       <c r="S11" t="n">
-        <v>0.106</v>
+        <v>0.384</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3514</v>
+        <v>-0.0453</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4574</v>
+        <v>0.4293</v>
       </c>
       <c r="V11" t="n">
         <v>-0.9405</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.7299</v>
+        <v>-3.7875</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.7327</v>
+        <v>-3.8744</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0028</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="G12" t="n">
         <v>-0.9302</v>
@@ -1390,13 +1390,13 @@
         <v>0.9919</v>
       </c>
       <c r="S12" t="n">
-        <v>0.3905</v>
+        <v>0.333</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0057</v>
+        <v>-0.136</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3848</v>
+        <v>0.469</v>
       </c>
       <c r="V12" t="n">
         <v>-1.2065</v>
@@ -1423,25 +1423,25 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-11.6178</v>
+        <v>-10.9476</v>
       </c>
       <c r="E13" t="n">
-        <v>-13.9109</v>
+        <v>-13.2875</v>
       </c>
       <c r="F13" t="n">
-        <v>2.2933</v>
+        <v>2.339999999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>-4.7696</v>
+        <v>-4.769600000000001</v>
       </c>
       <c r="H13" t="n">
         <v>-6.7775</v>
       </c>
       <c r="I13" t="n">
-        <v>2.008099999999999</v>
+        <v>2.0081</v>
       </c>
       <c r="J13" t="n">
-        <v>4.297899999999999</v>
+        <v>4.297900000000001</v>
       </c>
       <c r="K13" t="n">
         <v>-0.8509999999999998</v>
@@ -1450,7 +1450,7 @@
         <v>5.148999999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>-9.0672</v>
+        <v>-9.067200000000001</v>
       </c>
       <c r="N13" t="n">
         <v>-5.9264</v>
@@ -1468,13 +1468,13 @@
         <v>16.8626</v>
       </c>
       <c r="S13" t="n">
-        <v>3.8263</v>
+        <v>4.4964</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2275999999999998</v>
+        <v>0.8512</v>
       </c>
       <c r="U13" t="n">
-        <v>3.598399999999999</v>
+        <v>3.6451</v>
       </c>
       <c r="V13" t="n">
         <v>-6.7069</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. ROSA BEJARANO</t>
+          <t>G. GUTIÉRREZ MONREAL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.0712</v>
+        <v>3.9193</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8217</v>
+        <v>2.4398</v>
       </c>
       <c r="F14" t="n">
-        <v>3.2494</v>
+        <v>1.4795</v>
       </c>
       <c r="G14" t="n">
-        <v>1.285</v>
+        <v>1.6161</v>
       </c>
       <c r="H14" t="n">
-        <v>3.0094</v>
+        <v>0.2415</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.7244</v>
+        <v>1.3745</v>
       </c>
       <c r="J14" t="n">
-        <v>0.7771</v>
+        <v>1.9786</v>
       </c>
       <c r="K14" t="n">
-        <v>2.6571</v>
+        <v>0.7661</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.8799</v>
+        <v>1.2125</v>
       </c>
       <c r="M14" t="n">
-        <v>0.5079</v>
+        <v>-0.3626</v>
       </c>
       <c r="N14" t="n">
-        <v>0.3523</v>
+        <v>-0.5246</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1555</v>
+        <v>0.162</v>
       </c>
       <c r="P14" t="n">
-        <v>1.5871</v>
+        <v>1.9838</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.579</v>
+        <v>1.9838</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.0074</v>
+        <v>-0.5498</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1699</v>
+        <v>-0.408</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1626</v>
+        <v>-0.1418</v>
       </c>
       <c r="V14" t="n">
-        <v>1.2065</v>
+        <v>0.8692</v>
       </c>
       <c r="W14" t="n">
-        <v>1.2065</v>
+        <v>0.8692</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. ACOSTA ALMONTE</t>
+          <t>A. ROSA BEJARANO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.5779</v>
+        <v>3.9071</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.6546999999999999</v>
+        <v>0.4136</v>
       </c>
       <c r="F15" t="n">
-        <v>4.2325</v>
+        <v>3.4935</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.4331</v>
+        <v>1.285</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1006</v>
+        <v>3.0094</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.5337</v>
+        <v>-1.7244</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.3984</v>
+        <v>0.7771</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.5189</v>
+        <v>2.6571</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1205</v>
+        <v>-1.8799</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.0347</v>
+        <v>0.5079</v>
       </c>
       <c r="N15" t="n">
-        <v>0.6195000000000001</v>
+        <v>0.3523</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.6542</v>
+        <v>0.1555</v>
       </c>
       <c r="P15" t="n">
-        <v>0.7935</v>
+        <v>1.5871</v>
       </c>
       <c r="Q15" t="n">
         <v>-0.9919</v>
       </c>
       <c r="R15" t="n">
-        <v>1.7855</v>
+        <v>2.579</v>
       </c>
       <c r="S15" t="n">
-        <v>2.6855</v>
+        <v>-0.1714</v>
       </c>
       <c r="T15" t="n">
-        <v>0.6122</v>
+        <v>-0.5780999999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>2.0732</v>
+        <v>0.4066</v>
       </c>
       <c r="V15" t="n">
-        <v>0.532</v>
+        <v>1.2065</v>
       </c>
       <c r="W15" t="n">
-        <v>0.1234</v>
+        <v>1.2065</v>
       </c>
       <c r="X15" t="n">
-        <v>0.4085</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. GUTIÉRREZ MONREAL</t>
+          <t>P. MAJORAL DE LOS RIOS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.3309</v>
+        <v>2.9578</v>
       </c>
       <c r="E16" t="n">
-        <v>2.2358</v>
+        <v>-0.1697</v>
       </c>
       <c r="F16" t="n">
-        <v>1.0952</v>
+        <v>3.1275</v>
       </c>
       <c r="G16" t="n">
-        <v>1.6161</v>
+        <v>2.4969</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2415</v>
+        <v>1.9553</v>
       </c>
       <c r="I16" t="n">
-        <v>1.3745</v>
+        <v>0.5416</v>
       </c>
       <c r="J16" t="n">
-        <v>1.9786</v>
+        <v>2.3185</v>
       </c>
       <c r="K16" t="n">
-        <v>0.7661</v>
+        <v>0.9932</v>
       </c>
       <c r="L16" t="n">
-        <v>1.2125</v>
+        <v>1.3253</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.3626</v>
+        <v>0.1783</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.5246</v>
+        <v>0.962</v>
       </c>
       <c r="O16" t="n">
-        <v>0.162</v>
+        <v>-0.7837</v>
       </c>
       <c r="P16" t="n">
-        <v>1.9838</v>
+        <v>0.7935</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.9838</v>
       </c>
       <c r="R16" t="n">
-        <v>1.9838</v>
+        <v>2.7774</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.1382</v>
+        <v>-0.06660000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6121</v>
+        <v>-0.5044</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5261</v>
+        <v>0.4378</v>
       </c>
       <c r="V16" t="n">
-        <v>0.8692</v>
+        <v>-0.266</v>
       </c>
       <c r="W16" t="n">
-        <v>0.8692</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.3298</v>
+        <v>2.9181</v>
       </c>
       <c r="E17" t="n">
-        <v>2.2001</v>
+        <v>2.4042</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1297</v>
+        <v>0.514</v>
       </c>
       <c r="G17" t="n">
         <v>1.3834</v>
@@ -1780,13 +1780,13 @@
         <v>2.3806</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.5973</v>
+        <v>-1.0089</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.2356</v>
+        <v>-1.0315</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3617</v>
+        <v>0.0226</v>
       </c>
       <c r="V17" t="n">
         <v>2.1469</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. IGLESIAS GARCIA</t>
+          <t>O. BESORA TOMAS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.8745</v>
+        <v>2.5129</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6653</v>
+        <v>-0.4317</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2092</v>
+        <v>2.9445</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3002</v>
+        <v>-0.259</v>
       </c>
       <c r="H18" t="n">
-        <v>1.0582</v>
+        <v>-0.1863</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.758</v>
+        <v>-0.0727</v>
       </c>
       <c r="J18" t="n">
-        <v>0.9381</v>
+        <v>0.2922</v>
       </c>
       <c r="K18" t="n">
-        <v>1.0484</v>
+        <v>-0.6845</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.1103</v>
+        <v>0.9766</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.6379</v>
+        <v>-0.5512</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0098</v>
+        <v>0.4981</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-1.0493</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9919</v>
+        <v>1.1903</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9919</v>
+        <v>-1.9838</v>
       </c>
       <c r="R18" t="n">
-        <v>1.9838</v>
+        <v>3.1741</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6241</v>
+        <v>-0.2281</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4874</v>
+        <v>-0.5497</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1367</v>
+        <v>0.3216</v>
       </c>
       <c r="V18" t="n">
-        <v>1.2065</v>
+        <v>1.8097</v>
       </c>
       <c r="W18" t="n">
-        <v>1.2065</v>
+        <v>1.8097</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. MAJORAL DE LOS RIOS</t>
+          <t>A. IGLESIAS GARCIA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.7769</v>
+        <v>2.4008</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.5778</v>
+        <v>0.9713000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>2.3547</v>
+        <v>1.4295</v>
       </c>
       <c r="G19" t="n">
-        <v>2.4969</v>
+        <v>0.3002</v>
       </c>
       <c r="H19" t="n">
-        <v>1.9553</v>
+        <v>1.0582</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5416</v>
+        <v>-0.758</v>
       </c>
       <c r="J19" t="n">
-        <v>2.3185</v>
+        <v>0.9381</v>
       </c>
       <c r="K19" t="n">
-        <v>0.9932</v>
+        <v>1.0484</v>
       </c>
       <c r="L19" t="n">
-        <v>1.3253</v>
+        <v>-0.1103</v>
       </c>
       <c r="M19" t="n">
-        <v>0.1783</v>
+        <v>-0.6379</v>
       </c>
       <c r="N19" t="n">
-        <v>0.962</v>
+        <v>0.0098</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.7837</v>
+        <v>-0.6477000000000001</v>
       </c>
       <c r="P19" t="n">
-        <v>0.7935</v>
+        <v>0.9919</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9838</v>
+        <v>-0.9919</v>
       </c>
       <c r="R19" t="n">
-        <v>2.7774</v>
+        <v>1.9838</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.2475</v>
+        <v>-0.0978</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.9125</v>
+        <v>-0.1813</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3351</v>
+        <v>0.0835</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.266</v>
+        <v>1.2065</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.2065</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.266</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>O. BESORA TOMAS</t>
+          <t>D. ACOSTA ALMONTE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.0718</v>
+        <v>2.1478</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.0438</v>
+        <v>-1.2668</v>
       </c>
       <c r="F20" t="n">
-        <v>2.1156</v>
+        <v>3.4147</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.259</v>
+        <v>-0.4331</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.1863</v>
+        <v>0.1006</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.0727</v>
+        <v>-0.5337</v>
       </c>
       <c r="J20" t="n">
-        <v>0.2922</v>
+        <v>-0.3984</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.6845</v>
+        <v>-0.5189</v>
       </c>
       <c r="L20" t="n">
-        <v>0.9766</v>
+        <v>0.1205</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.5512</v>
+        <v>-0.0347</v>
       </c>
       <c r="N20" t="n">
-        <v>0.4981</v>
+        <v>0.6195000000000001</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.0493</v>
+        <v>-0.6542</v>
       </c>
       <c r="P20" t="n">
-        <v>1.1903</v>
+        <v>0.7935</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9838</v>
+        <v>-0.9919</v>
       </c>
       <c r="R20" t="n">
-        <v>3.1741</v>
+        <v>1.7855</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.6692</v>
+        <v>1.2555</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.1619</v>
+        <v>0.0001</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5074</v>
+        <v>1.2554</v>
       </c>
       <c r="V20" t="n">
-        <v>1.8097</v>
+        <v>0.532</v>
       </c>
       <c r="W20" t="n">
-        <v>1.8097</v>
+        <v>0.1234</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>0.4085</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.5151</v>
+        <v>1.2233</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.3746</v>
+        <v>0.0335</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8897</v>
+        <v>1.1898</v>
       </c>
       <c r="G21" t="n">
         <v>1.273</v>
@@ -2092,13 +2092,13 @@
         <v>1.5871</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3611</v>
+        <v>0.3471</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4988</v>
+        <v>-0.0906</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1376</v>
+        <v>0.4378</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.5531</v>
+        <v>-1.7512</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.6167</v>
+        <v>-1.9228</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0636</v>
+        <v>0.1716</v>
       </c>
       <c r="G22" t="n">
         <v>-1.0554</v>
@@ -2170,13 +2170,13 @@
         <v>0.9919</v>
       </c>
       <c r="S22" t="n">
-        <v>0.157</v>
+        <v>-0.0411</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2438</v>
+        <v>-0.0623</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0868</v>
+        <v>0.0212</v>
       </c>
       <c r="V22" t="n">
         <v>0.3373</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.3771</v>
+        <v>-5.8974</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.9485</v>
+        <v>-4.7648</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.4285</v>
+        <v>-1.1326</v>
       </c>
       <c r="G23" t="n">
         <v>-1.8375</v>
@@ -2248,13 +2248,13 @@
         <v>1.5871</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0238</v>
+        <v>-0.5442</v>
       </c>
       <c r="T23" t="n">
-        <v>0.6236</v>
+        <v>-0.1926</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.6474</v>
+        <v>-0.3515</v>
       </c>
       <c r="V23" t="n">
         <v>-1.1352</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>11.6179</v>
+        <v>14.3385</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.293200000000001</v>
+        <v>-2.293400000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>13.9111</v>
+        <v>16.632</v>
       </c>
       <c r="G24" t="n">
         <v>4.769600000000001</v>
@@ -2326,13 +2326,13 @@
         <v>20.8303</v>
       </c>
       <c r="S24" t="n">
-        <v>-3.8261</v>
+        <v>-1.1053</v>
       </c>
       <c r="T24" t="n">
-        <v>-3.5986</v>
+        <v>-3.5984</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2278</v>
+        <v>2.4932</v>
       </c>
       <c r="V24" t="n">
         <v>6.706899999999999</v>
